--- a/data/台股_警戒掃描.xlsx
+++ b/data/台股_警戒掃描.xlsx
@@ -472,12 +472,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>30d 72798 股, 最新日 23 股</t>
+          <t>30d 75369 股, 最新日 60 股</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -505,12 +505,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>30d 94442 股, 最新日 901 股</t>
+          <t>30d 93715 股, 最新日 1100 股</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -538,12 +538,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>30d 80639 股, 最新日 2948 股</t>
+          <t>30d 70090 股, 最新日 251 股</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -571,12 +571,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30d 155618 股, 最新日 392 股</t>
+          <t>30d 173418 股, 最新日 410 股</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -604,12 +604,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>30d 86111 股, 最新日 150 股</t>
+          <t>30d 82096 股, 最新日 16 股</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -637,12 +637,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>30d 137246 股, 最新日 150 股</t>
+          <t>30d 116218 股, 最新日 2412 股</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -670,12 +670,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>30d 90537 股, 最新日 4000 股</t>
+          <t>30d 87727 股, 最新日 3124 股</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -703,12 +703,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>30d 89933 股, 最新日 295 股</t>
+          <t>30d 111574 股, 最新日 5757 股</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -736,12 +736,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>30d 61819 股, 最新日 3 股</t>
+          <t>30d 93407 股, 最新日 1302 股</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -769,12 +769,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>30d 105507 股, 最新日 250 股</t>
+          <t>30d 128798 股, 最新日 34 股</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -802,12 +802,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>30d 56415 股, 最新日 541 股</t>
+          <t>30d 67252 股, 最新日 188 股</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -828,7 +828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C100"/>
+  <dimension ref="A1:C99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -855,101 +855,101 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>155618</v>
+        <v>173418</v>
       </c>
       <c r="C2" t="n">
-        <v>392</v>
+        <v>410</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>137246</v>
+        <v>128798</v>
       </c>
       <c r="C3" t="n">
-        <v>150</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>105507</v>
+        <v>116218</v>
       </c>
       <c r="C4" t="n">
-        <v>250</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>94442</v>
+        <v>111574</v>
       </c>
       <c r="C5" t="n">
-        <v>901</v>
+        <v>5757</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>90537</v>
+        <v>93715</v>
       </c>
       <c r="C6" t="n">
-        <v>4000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>89933</v>
+        <v>93407</v>
       </c>
       <c r="C7" t="n">
-        <v>295</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>86111</v>
+        <v>87727</v>
       </c>
       <c r="C8" t="n">
-        <v>150</v>
+        <v>3124</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80639</v>
+        <v>82096</v>
       </c>
       <c r="C9" t="n">
-        <v>2948</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -959,23 +959,23 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>72798</v>
+        <v>75369</v>
       </c>
       <c r="C10" t="n">
-        <v>23</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>61819</v>
+        <v>70090</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>56415</v>
+        <v>67252</v>
       </c>
       <c r="C12" t="n">
-        <v>541</v>
+        <v>188</v>
       </c>
     </row>
     <row r="13">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>42024</v>
+        <v>41110</v>
       </c>
       <c r="C13" t="n">
-        <v>13</v>
+        <v>300</v>
       </c>
     </row>
     <row r="14">
@@ -1011,75 +1011,75 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>38737</v>
+        <v>40160</v>
       </c>
       <c r="C14" t="n">
-        <v>341</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21777</v>
+        <v>23978</v>
       </c>
       <c r="C15" t="n">
-        <v>491</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>19750</v>
+        <v>19587</v>
       </c>
       <c r="C16" t="n">
-        <v>1382</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18120</v>
+        <v>19299</v>
       </c>
       <c r="C17" t="n">
-        <v>1747</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16076</v>
+        <v>18557</v>
       </c>
       <c r="C18" t="n">
-        <v>14</v>
+        <v>308</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16000</v>
+        <v>15903</v>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1089,241 +1089,241 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>15628</v>
+        <v>14532</v>
       </c>
       <c r="C20" t="n">
-        <v>422</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15415</v>
+        <v>14393</v>
       </c>
       <c r="C21" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>13795</v>
+        <v>14152</v>
       </c>
       <c r="C22" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13468</v>
+        <v>13039</v>
       </c>
       <c r="C23" t="n">
-        <v>730</v>
+        <v>191</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>11744</v>
+        <v>12666</v>
       </c>
       <c r="C24" t="n">
-        <v>794</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10912</v>
+        <v>12203</v>
       </c>
       <c r="C25" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>10888</v>
+        <v>11245</v>
       </c>
       <c r="C26" t="n">
-        <v>100</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10659</v>
+        <v>10779</v>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10530</v>
+        <v>10389</v>
       </c>
       <c r="C28" t="n">
-        <v>13</v>
+        <v>88</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>10363</v>
+        <v>9906</v>
       </c>
       <c r="C29" t="n">
-        <v>23</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>10019</v>
+        <v>9864</v>
       </c>
       <c r="C30" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>9909</v>
+        <v>9605</v>
       </c>
       <c r="C31" t="n">
-        <v>256</v>
+        <v>485</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>9029</v>
+        <v>8101</v>
       </c>
       <c r="C32" t="n">
-        <v>74</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>8589</v>
+        <v>7731</v>
       </c>
       <c r="C33" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>6563</v>
+        <v>6540</v>
       </c>
       <c r="C34" t="n">
-        <v>192</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>6495</v>
+        <v>6364</v>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>6268</v>
+        <v>6205</v>
       </c>
       <c r="C36" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>5748</v>
+        <v>6032</v>
       </c>
       <c r="C37" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>5290</v>
+        <v>5914</v>
       </c>
       <c r="C38" t="n">
         <v>3</v>
@@ -1332,92 +1332,92 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>5218</v>
+        <v>5824</v>
       </c>
       <c r="C39" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>5176</v>
+        <v>5264</v>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4743</v>
+        <v>5172</v>
       </c>
       <c r="C41" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4551</v>
+        <v>5152</v>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>562</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4511</v>
+        <v>5074</v>
       </c>
       <c r="C43" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4467</v>
+        <v>4572</v>
       </c>
       <c r="C44" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4439</v>
+        <v>4451</v>
       </c>
       <c r="C45" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -1427,322 +1427,322 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4395</v>
+        <v>4255</v>
       </c>
       <c r="C46" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4160</v>
+        <v>3725</v>
       </c>
       <c r="C47" t="n">
-        <v>219</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4134</v>
+        <v>3521</v>
       </c>
       <c r="C48" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4117</v>
+        <v>3409</v>
       </c>
       <c r="C49" t="n">
-        <v>130</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3590</v>
+        <v>3331</v>
       </c>
       <c r="C50" t="n">
-        <v>307</v>
+        <v>41</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3582</v>
+        <v>2934</v>
       </c>
       <c r="C51" t="n">
-        <v>257</v>
+        <v>32</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3311</v>
+        <v>2752</v>
       </c>
       <c r="C52" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3253</v>
+        <v>2709</v>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3230</v>
+        <v>2665</v>
       </c>
       <c r="C54" t="n">
-        <v>12</v>
+        <v>75</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2869</v>
+        <v>2632</v>
       </c>
       <c r="C55" t="n">
-        <v>414</v>
+        <v>30</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2809</v>
+        <v>2576</v>
       </c>
       <c r="C56" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2804</v>
+        <v>2523</v>
       </c>
       <c r="C57" t="n">
-        <v>300</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2610</v>
+        <v>2472</v>
       </c>
       <c r="C58" t="n">
-        <v>113</v>
+        <v>40</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2474</v>
+        <v>2363</v>
       </c>
       <c r="C59" t="n">
-        <v>88</v>
+        <v>40</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2459</v>
+        <v>2300</v>
       </c>
       <c r="C60" t="n">
-        <v>34</v>
+        <v>240</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2320</v>
+        <v>2296</v>
       </c>
       <c r="C61" t="n">
-        <v>35</v>
+        <v>190</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2246</v>
+        <v>2143</v>
       </c>
       <c r="C62" t="n">
-        <v>91</v>
+        <v>36</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2194</v>
+        <v>2042</v>
       </c>
       <c r="C63" t="n">
-        <v>33</v>
+        <v>420</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2192</v>
+        <v>1918</v>
       </c>
       <c r="C64" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2160</v>
+        <v>1905</v>
       </c>
       <c r="C65" t="n">
-        <v>45</v>
+        <v>585</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2120</v>
+        <v>1775</v>
       </c>
       <c r="C66" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1939</v>
+        <v>1773</v>
       </c>
       <c r="C67" t="n">
-        <v>150</v>
+        <v>246</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1928</v>
+        <v>1745</v>
       </c>
       <c r="C68" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1799</v>
+        <v>1731</v>
       </c>
       <c r="C69" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1744</v>
+        <v>1526</v>
       </c>
       <c r="C70" t="n">
-        <v>27</v>
+        <v>100</v>
       </c>
     </row>
     <row r="71">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1514</v>
+        <v>1489</v>
       </c>
       <c r="C71" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
     </row>
     <row r="72">
@@ -1765,36 +1765,36 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1371</v>
+        <v>1437</v>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>123</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1250</v>
+        <v>853</v>
       </c>
       <c r="C73" t="n">
-        <v>2</v>
+        <v>502</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1055</v>
+        <v>826</v>
       </c>
       <c r="C74" t="n">
-        <v>150</v>
+        <v>24</v>
       </c>
     </row>
     <row r="75">
@@ -1804,166 +1804,166 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>872</v>
+        <v>796</v>
       </c>
       <c r="C75" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>867</v>
+        <v>778</v>
       </c>
       <c r="C76" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>853</v>
+        <v>758</v>
       </c>
       <c r="C77" t="n">
-        <v>502</v>
+        <v>65</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>761</v>
+        <v>614</v>
       </c>
       <c r="C78" t="n">
-        <v>90</v>
+        <v>151</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>693</v>
+        <v>576</v>
       </c>
       <c r="C79" t="n">
-        <v>693</v>
+        <v>10</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>585</v>
+        <v>531</v>
       </c>
       <c r="C80" t="n">
-        <v>69</v>
+        <v>50</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>532</v>
+        <v>466</v>
       </c>
       <c r="C81" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>530</v>
+        <v>448</v>
       </c>
       <c r="C82" t="n">
-        <v>132</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C83" t="n">
-        <v>189</v>
+        <v>71</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>402</v>
+        <v>340</v>
       </c>
       <c r="C84" t="n">
-        <v>125</v>
+        <v>26</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>373</v>
+        <v>338</v>
       </c>
       <c r="C85" t="n">
-        <v>26</v>
+        <v>132</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>370</v>
+        <v>258</v>
       </c>
       <c r="C86" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>345</v>
+        <v>183</v>
       </c>
       <c r="C87" t="n">
-        <v>103</v>
+        <v>24</v>
       </c>
     </row>
     <row r="88">
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>258</v>
+        <v>182</v>
       </c>
       <c r="C88" t="n">
         <v>89</v>
@@ -1982,79 +1982,79 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>228</v>
+        <v>173</v>
       </c>
       <c r="C89" t="n">
-        <v>94</v>
+        <v>42</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>222</v>
+        <v>169</v>
       </c>
       <c r="C90" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>211</v>
+        <v>163</v>
       </c>
       <c r="C91" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>203</v>
+        <v>133</v>
       </c>
       <c r="C92" t="n">
-        <v>100</v>
+        <v>24</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>125</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="C94" t="n">
-        <v>61</v>
+        <v>94</v>
       </c>
     </row>
     <row r="95">
@@ -2064,74 +2064,61 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="C95" t="n">
-        <v>20</v>
+        <v>66</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="C96" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="C97" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C98" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C99" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>5478</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>3</v>
-      </c>
-      <c r="C100" t="n">
         <v>3</v>
       </c>
     </row>

--- a/data/台股_警戒掃描.xlsx
+++ b/data/台股_警戒掃描.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,12 +472,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>30d 75369 股, 最新日 60 股</t>
+          <t>30d 86750 股, 最新日 100 股</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -505,12 +505,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>30d 93715 股, 最新日 1100 股</t>
+          <t>30d 77007 股, 最新日 77 股</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -538,12 +538,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>30d 70090 股, 最新日 251 股</t>
+          <t>30d 67689 股, 最新日 20 股</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -556,12 +556,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -571,30 +571,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30d 173418 股, 最新日 410 股</t>
+          <t>30d 147686 股, 最新日 1500 股</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -604,30 +604,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>30d 82096 股, 最新日 16 股</t>
+          <t>30d 142089 股, 最新日 266 股</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -637,12 +637,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>30d 116218 股, 最新日 2412 股</t>
+          <t>30d 69888 股, 最新日 473 股</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -655,12 +655,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -670,30 +670,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>30d 87727 股, 最新日 3124 股</t>
+          <t>30d 108187 股, 最新日 100 股</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -703,30 +703,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>30d 111574 股, 最新日 5757 股</t>
+          <t>30d 86926 股, 最新日 28 股</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -736,30 +736,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>30d 93407 股, 最新日 1302 股</t>
+          <t>30d 76838 股, 最新日 250 股</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -769,30 +769,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>30d 128798 股, 最新日 34 股</t>
+          <t>30d 132240 股, 最新日 150 股</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -802,16 +802,82 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>30d 67252 股, 最新日 188 股</t>
+          <t>30d 86306 股, 最新日 4 股</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>🪦 借券爆量</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>30d 144237 股, 最新日 80 股</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>🪦 借券爆量</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>30d 65871 股, 最新日 65 股</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -828,7 +894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C99"/>
+  <dimension ref="A1:C102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -851,14 +917,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>173418</v>
+        <v>147686</v>
       </c>
       <c r="C2" t="n">
-        <v>410</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="3">
@@ -868,23 +934,23 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>128798</v>
+        <v>144237</v>
       </c>
       <c r="C3" t="n">
-        <v>34</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>116218</v>
+        <v>142089</v>
       </c>
       <c r="C4" t="n">
-        <v>2412</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5">
@@ -894,179 +960,179 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>111574</v>
+        <v>132240</v>
       </c>
       <c r="C5" t="n">
-        <v>5757</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>93715</v>
+        <v>108187</v>
       </c>
       <c r="C6" t="n">
-        <v>1100</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>93407</v>
+        <v>86926</v>
       </c>
       <c r="C7" t="n">
-        <v>1302</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>87727</v>
+        <v>86750</v>
       </c>
       <c r="C8" t="n">
-        <v>3124</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>82096</v>
+        <v>86306</v>
       </c>
       <c r="C9" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>75369</v>
+        <v>77007</v>
       </c>
       <c r="C10" t="n">
-        <v>60</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>70090</v>
+        <v>76838</v>
       </c>
       <c r="C11" t="n">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>67252</v>
+        <v>69888</v>
       </c>
       <c r="C12" t="n">
-        <v>188</v>
+        <v>473</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>41110</v>
+        <v>67689</v>
       </c>
       <c r="C13" t="n">
-        <v>300</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>40160</v>
+        <v>65871</v>
       </c>
       <c r="C14" t="n">
-        <v>1587</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23978</v>
+        <v>22047</v>
       </c>
       <c r="C15" t="n">
-        <v>31</v>
+        <v>186</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>19587</v>
+        <v>21317</v>
       </c>
       <c r="C16" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19299</v>
+        <v>21110</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18557</v>
+        <v>20863</v>
       </c>
       <c r="C18" t="n">
-        <v>308</v>
+        <v>226</v>
       </c>
     </row>
     <row r="19">
@@ -1076,49 +1142,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15903</v>
+        <v>17749</v>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>14532</v>
+        <v>17366</v>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14393</v>
+        <v>16090</v>
       </c>
       <c r="C21" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>14152</v>
+        <v>15136</v>
       </c>
       <c r="C22" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23">
@@ -1128,270 +1194,270 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13039</v>
+        <v>12251</v>
       </c>
       <c r="C23" t="n">
-        <v>191</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>12666</v>
+        <v>12222</v>
       </c>
       <c r="C24" t="n">
-        <v>67</v>
+        <v>240</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>12203</v>
+        <v>11280</v>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>11245</v>
+        <v>11145</v>
       </c>
       <c r="C26" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10779</v>
+        <v>11057</v>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10389</v>
+        <v>11053</v>
       </c>
       <c r="C28" t="n">
-        <v>88</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>9906</v>
+        <v>10988</v>
       </c>
       <c r="C29" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>9864</v>
+        <v>10920</v>
       </c>
       <c r="C30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>9605</v>
+        <v>10821</v>
       </c>
       <c r="C31" t="n">
-        <v>485</v>
+        <v>825</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>8101</v>
+        <v>9808</v>
       </c>
       <c r="C32" t="n">
-        <v>47</v>
+        <v>618</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7731</v>
+        <v>9753</v>
       </c>
       <c r="C33" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>6540</v>
+        <v>9015</v>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>257</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>6364</v>
+        <v>7531</v>
       </c>
       <c r="C35" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>6205</v>
+        <v>7036</v>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>200</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>6032</v>
+        <v>6751</v>
       </c>
       <c r="C37" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>5914</v>
+        <v>6706</v>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>5824</v>
+        <v>6248</v>
       </c>
       <c r="C39" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>5264</v>
+        <v>5925</v>
       </c>
       <c r="C40" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>5172</v>
+        <v>5832</v>
       </c>
       <c r="C41" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>5152</v>
+        <v>4765</v>
       </c>
       <c r="C42" t="n">
-        <v>562</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>5074</v>
+        <v>4434</v>
       </c>
       <c r="C43" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="44">
@@ -1401,10 +1467,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4572</v>
+        <v>4419</v>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45">
@@ -1414,127 +1480,127 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4451</v>
+        <v>4126</v>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4255</v>
+        <v>3449</v>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>75</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3725</v>
+        <v>3417</v>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3521</v>
+        <v>3402</v>
       </c>
       <c r="C48" t="n">
-        <v>16</v>
+        <v>56</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3409</v>
+        <v>3318</v>
       </c>
       <c r="C49" t="n">
-        <v>15</v>
+        <v>95</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3331</v>
+        <v>3279</v>
       </c>
       <c r="C50" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2934</v>
+        <v>3255</v>
       </c>
       <c r="C51" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2752</v>
+        <v>3187</v>
       </c>
       <c r="C52" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2709</v>
+        <v>3013</v>
       </c>
       <c r="C53" t="n">
-        <v>70</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2665</v>
+        <v>2798</v>
       </c>
       <c r="C54" t="n">
-        <v>75</v>
+        <v>137</v>
       </c>
     </row>
     <row r="55">
@@ -1544,36 +1610,36 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2632</v>
+        <v>2771</v>
       </c>
       <c r="C55" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2576</v>
+        <v>2757</v>
       </c>
       <c r="C56" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2523</v>
+        <v>2729</v>
       </c>
       <c r="C57" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -1583,23 +1649,23 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2472</v>
+        <v>2715</v>
       </c>
       <c r="C58" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2363</v>
+        <v>2509</v>
       </c>
       <c r="C59" t="n">
-        <v>40</v>
+        <v>135</v>
       </c>
     </row>
     <row r="60">
@@ -1609,49 +1675,49 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2300</v>
+        <v>2065</v>
       </c>
       <c r="C60" t="n">
-        <v>240</v>
+        <v>79</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2296</v>
+        <v>2009</v>
       </c>
       <c r="C61" t="n">
-        <v>190</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2143</v>
+        <v>1990</v>
       </c>
       <c r="C62" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2042</v>
+        <v>1985</v>
       </c>
       <c r="C63" t="n">
-        <v>420</v>
+        <v>49</v>
       </c>
     </row>
     <row r="64">
@@ -1661,166 +1727,166 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1918</v>
+        <v>1959</v>
       </c>
       <c r="C64" t="n">
-        <v>18</v>
+        <v>61</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1905</v>
+        <v>1791</v>
       </c>
       <c r="C65" t="n">
-        <v>585</v>
+        <v>351</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1775</v>
+        <v>1733</v>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>150</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1773</v>
+        <v>1694</v>
       </c>
       <c r="C67" t="n">
-        <v>246</v>
+        <v>62</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1745</v>
+        <v>1515</v>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>82</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1731</v>
+        <v>1506</v>
       </c>
       <c r="C69" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1526</v>
+        <v>1489</v>
       </c>
       <c r="C70" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1489</v>
+        <v>1416</v>
       </c>
       <c r="C71" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1437</v>
+        <v>1070</v>
       </c>
       <c r="C72" t="n">
-        <v>123</v>
+        <v>85</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>853</v>
+        <v>1000</v>
       </c>
       <c r="C73" t="n">
-        <v>502</v>
+        <v>22</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>826</v>
+        <v>907</v>
       </c>
       <c r="C74" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>796</v>
+        <v>884</v>
       </c>
       <c r="C75" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>778</v>
+        <v>800</v>
       </c>
       <c r="C76" t="n">
-        <v>27</v>
+        <v>99</v>
       </c>
     </row>
     <row r="77">
@@ -1839,105 +1905,105 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>614</v>
+        <v>737</v>
       </c>
       <c r="C78" t="n">
-        <v>151</v>
+        <v>43</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>576</v>
+        <v>694</v>
       </c>
       <c r="C79" t="n">
-        <v>10</v>
+        <v>502</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>531</v>
+        <v>626</v>
       </c>
       <c r="C80" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>466</v>
+        <v>606</v>
       </c>
       <c r="C81" t="n">
-        <v>61</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>448</v>
+        <v>472</v>
       </c>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>416</v>
+        <v>391</v>
       </c>
       <c r="C83" t="n">
-        <v>71</v>
+        <v>26</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>340</v>
+        <v>318</v>
       </c>
       <c r="C84" t="n">
-        <v>26</v>
+        <v>132</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>338</v>
+        <v>262</v>
       </c>
       <c r="C85" t="n">
-        <v>132</v>
+        <v>60</v>
       </c>
     </row>
     <row r="86">
@@ -1956,53 +2022,53 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>183</v>
+        <v>251</v>
       </c>
       <c r="C87" t="n">
-        <v>24</v>
+        <v>49</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>182</v>
+        <v>232</v>
       </c>
       <c r="C88" t="n">
-        <v>89</v>
+        <v>58</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="C89" t="n">
-        <v>42</v>
+        <v>104</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91">
@@ -2021,11 +2087,11 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="C92" t="n">
         <v>24</v>
@@ -2034,27 +2100,27 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="C93" t="n">
-        <v>125</v>
+        <v>6</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="C94" t="n">
-        <v>94</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95">
@@ -2064,62 +2130,101 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="C95" t="n">
-        <v>66</v>
+        <v>37</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="C96" t="n">
-        <v>68</v>
+        <v>125</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>36</v>
+        <v>121</v>
       </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="C98" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="C99" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>5225</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>39</v>
+      </c>
+      <c r="C100" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>6690</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>19</v>
+      </c>
+      <c r="C101" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2640</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>6</v>
+      </c>
+      <c r="C102" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/data/台股_警戒掃描.xlsx
+++ b/data/台股_警戒掃描.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,12 +457,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -472,30 +472,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>30d 86750 股, 最新日 100 股</t>
+          <t>30d 69080 股, 最新日 20 股</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -505,30 +505,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>30d 77007 股, 最新日 77 股</t>
+          <t>30d 80557 股, 最新日 6 股</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -538,30 +538,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>30d 67689 股, 最新日 20 股</t>
+          <t>30d 201038 股, 最新日 225 股</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -571,30 +571,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30d 147686 股, 最新日 1500 股</t>
+          <t>30d 150474 股, 最新日 788 股</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -604,30 +604,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>30d 142089 股, 最新日 266 股</t>
+          <t>30d 73400 股, 最新日 64 股</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -637,12 +637,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>30d 69888 股, 最新日 473 股</t>
+          <t>30d 125391 股, 最新日 388 股</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -655,12 +655,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -670,30 +670,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>30d 108187 股, 最新日 100 股</t>
+          <t>30d 85674 股, 最新日 76 股</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -703,12 +703,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>30d 86926 股, 最新日 28 股</t>
+          <t>30d 78180 股, 最新日 108 股</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -721,12 +721,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -736,30 +736,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>30d 76838 股, 最新日 250 股</t>
+          <t>30d 145752 股, 最新日 180 股</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -769,12 +769,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>30d 132240 股, 最新日 150 股</t>
+          <t>30d 72445 股, 最新日 1789 股</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -787,12 +787,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -802,30 +802,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>30d 86306 股, 最新日 4 股</t>
+          <t>30d 156136 股, 最新日 5 股</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -835,49 +835,16 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>30d 144237 股, 最新日 80 股</t>
+          <t>30d 61100 股, 最新日 34 股</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>🪦 借券爆量</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>30d 65871 股, 最新日 65 股</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -894,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C102"/>
+  <dimension ref="A1:C103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -921,10 +888,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>147686</v>
+        <v>201038</v>
       </c>
       <c r="C2" t="n">
-        <v>1500</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3">
@@ -934,10 +901,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>144237</v>
+        <v>156136</v>
       </c>
       <c r="C3" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -947,10 +914,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>142089</v>
+        <v>150474</v>
       </c>
       <c r="C4" t="n">
-        <v>266</v>
+        <v>788</v>
       </c>
     </row>
     <row r="5">
@@ -960,10 +927,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>132240</v>
+        <v>145752</v>
       </c>
       <c r="C5" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6">
@@ -973,10 +940,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>108187</v>
+        <v>125391</v>
       </c>
       <c r="C6" t="n">
-        <v>100</v>
+        <v>388</v>
       </c>
     </row>
     <row r="7">
@@ -986,101 +953,101 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>86926</v>
+        <v>85674</v>
       </c>
       <c r="C7" t="n">
-        <v>28</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>86750</v>
+        <v>80557</v>
       </c>
       <c r="C8" t="n">
-        <v>100</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>86306</v>
+        <v>78180</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>77007</v>
+        <v>73400</v>
       </c>
       <c r="C10" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>76838</v>
+        <v>72445</v>
       </c>
       <c r="C11" t="n">
-        <v>250</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>69888</v>
+        <v>69080</v>
       </c>
       <c r="C12" t="n">
-        <v>473</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>67689</v>
+        <v>61100</v>
       </c>
       <c r="C13" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>65871</v>
+        <v>38995</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1057,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22047</v>
+        <v>24304</v>
       </c>
       <c r="C15" t="n">
-        <v>186</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16">
@@ -1103,10 +1070,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>21317</v>
+        <v>21487</v>
       </c>
       <c r="C16" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
@@ -1116,140 +1083,140 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>21110</v>
+        <v>20751</v>
       </c>
       <c r="C17" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20863</v>
+        <v>16803</v>
       </c>
       <c r="C18" t="n">
-        <v>226</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17749</v>
+        <v>16623</v>
       </c>
       <c r="C19" t="n">
-        <v>100</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17366</v>
+        <v>16294</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16090</v>
+        <v>15333</v>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>198</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>15136</v>
+        <v>14074</v>
       </c>
       <c r="C22" t="n">
-        <v>25</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>12251</v>
+        <v>13915</v>
       </c>
       <c r="C23" t="n">
-        <v>69</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>12222</v>
+        <v>12674</v>
       </c>
       <c r="C24" t="n">
-        <v>240</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>11280</v>
+        <v>12624</v>
       </c>
       <c r="C25" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>11145</v>
+        <v>11916</v>
       </c>
       <c r="C26" t="n">
-        <v>30</v>
+        <v>232</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>11057</v>
+        <v>11192</v>
       </c>
       <c r="C27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28">
@@ -1259,10 +1226,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>11053</v>
+        <v>10652</v>
       </c>
       <c r="C28" t="n">
-        <v>16</v>
+        <v>187</v>
       </c>
     </row>
     <row r="29">
@@ -1272,176 +1239,176 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>10988</v>
+        <v>9486</v>
       </c>
       <c r="C29" t="n">
-        <v>75</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>10920</v>
+        <v>9379</v>
       </c>
       <c r="C30" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>10821</v>
+        <v>8402</v>
       </c>
       <c r="C31" t="n">
-        <v>825</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>9808</v>
+        <v>8155</v>
       </c>
       <c r="C32" t="n">
-        <v>618</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>9753</v>
+        <v>7576</v>
       </c>
       <c r="C33" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>9015</v>
+        <v>7000</v>
       </c>
       <c r="C34" t="n">
-        <v>257</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>7531</v>
+        <v>6806</v>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>7036</v>
+        <v>6719</v>
       </c>
       <c r="C36" t="n">
-        <v>200</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>6751</v>
+        <v>6173</v>
       </c>
       <c r="C37" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>6706</v>
+        <v>5766</v>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
+        <v>156</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>6248</v>
+        <v>5462</v>
       </c>
       <c r="C39" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>5925</v>
+        <v>5365</v>
       </c>
       <c r="C40" t="n">
-        <v>41</v>
+        <v>85</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>5832</v>
+        <v>5325</v>
       </c>
       <c r="C41" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4765</v>
+        <v>5053</v>
       </c>
       <c r="C42" t="n">
         <v>4</v>
@@ -1450,128 +1417,128 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4434</v>
+        <v>4752</v>
       </c>
       <c r="C43" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4419</v>
+        <v>3962</v>
       </c>
       <c r="C44" t="n">
-        <v>21</v>
+        <v>393</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4126</v>
+        <v>3840</v>
       </c>
       <c r="C45" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3449</v>
+        <v>3619</v>
       </c>
       <c r="C46" t="n">
-        <v>75</v>
+        <v>94</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3417</v>
+        <v>3526</v>
       </c>
       <c r="C47" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3402</v>
+        <v>3357</v>
       </c>
       <c r="C48" t="n">
-        <v>56</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3318</v>
+        <v>3298</v>
       </c>
       <c r="C49" t="n">
-        <v>95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3279</v>
+        <v>3051</v>
       </c>
       <c r="C50" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3255</v>
+        <v>3006</v>
       </c>
       <c r="C51" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3187</v>
+        <v>3006</v>
       </c>
       <c r="C52" t="n">
         <v>24</v>
@@ -1580,79 +1547,79 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3013</v>
+        <v>2850</v>
       </c>
       <c r="C53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2798</v>
+        <v>2757</v>
       </c>
       <c r="C54" t="n">
-        <v>137</v>
+        <v>38</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2771</v>
+        <v>2690</v>
       </c>
       <c r="C55" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2757</v>
+        <v>2612</v>
       </c>
       <c r="C56" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2729</v>
+        <v>2527</v>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2715</v>
+        <v>2335</v>
       </c>
       <c r="C58" t="n">
-        <v>8</v>
+        <v>418</v>
       </c>
     </row>
     <row r="59">
@@ -1662,10 +1629,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2509</v>
+        <v>2106</v>
       </c>
       <c r="C59" t="n">
-        <v>135</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -1675,75 +1642,75 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2065</v>
+        <v>2097</v>
       </c>
       <c r="C60" t="n">
-        <v>79</v>
+        <v>133</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2009</v>
+        <v>2060</v>
       </c>
       <c r="C61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1990</v>
+        <v>2049</v>
       </c>
       <c r="C62" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1985</v>
+        <v>1999</v>
       </c>
       <c r="C63" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1959</v>
+        <v>1925</v>
       </c>
       <c r="C64" t="n">
-        <v>61</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1791</v>
+        <v>1669</v>
       </c>
       <c r="C65" t="n">
-        <v>351</v>
+        <v>171</v>
       </c>
     </row>
     <row r="66">
@@ -1753,101 +1720,101 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1733</v>
+        <v>1600</v>
       </c>
       <c r="C66" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1694</v>
+        <v>1521</v>
       </c>
       <c r="C67" t="n">
-        <v>62</v>
+        <v>140</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1515</v>
+        <v>1512</v>
       </c>
       <c r="C68" t="n">
-        <v>82</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="C69" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1489</v>
+        <v>1372</v>
       </c>
       <c r="C70" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1416</v>
+        <v>1370</v>
       </c>
       <c r="C71" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1070</v>
+        <v>1313</v>
       </c>
       <c r="C72" t="n">
-        <v>85</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1000</v>
+        <v>1091</v>
       </c>
       <c r="C73" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
@@ -1870,88 +1837,88 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>884</v>
+        <v>901</v>
       </c>
       <c r="C75" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="C76" t="n">
-        <v>99</v>
+        <v>187</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>758</v>
+        <v>769</v>
       </c>
       <c r="C77" t="n">
-        <v>65</v>
+        <v>83</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>737</v>
+        <v>694</v>
       </c>
       <c r="C78" t="n">
-        <v>43</v>
+        <v>502</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>694</v>
+        <v>660</v>
       </c>
       <c r="C79" t="n">
-        <v>502</v>
+        <v>54</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>626</v>
+        <v>648</v>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>606</v>
+        <v>472</v>
       </c>
       <c r="C81" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
     </row>
     <row r="82">
@@ -1961,218 +1928,218 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>472</v>
+        <v>420</v>
       </c>
       <c r="C82" t="n">
-        <v>3</v>
+        <v>81</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>391</v>
+        <v>336</v>
       </c>
       <c r="C83" t="n">
-        <v>26</v>
+        <v>49</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>318</v>
+        <v>305</v>
       </c>
       <c r="C84" t="n">
-        <v>132</v>
+        <v>54</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>262</v>
+        <v>291</v>
       </c>
       <c r="C85" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>258</v>
+        <v>287</v>
       </c>
       <c r="C86" t="n">
-        <v>32</v>
+        <v>100</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="C87" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>232</v>
+        <v>258</v>
       </c>
       <c r="C88" t="n">
-        <v>58</v>
+        <v>32</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="C89" t="n">
-        <v>104</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>182</v>
+        <v>163</v>
       </c>
       <c r="C90" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>163</v>
+        <v>140</v>
       </c>
       <c r="C91" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="C92" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C93" t="n">
-        <v>6</v>
+        <v>37</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="C94" t="n">
-        <v>5</v>
+        <v>125</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="C95" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>125</v>
+        <v>74</v>
       </c>
       <c r="C96" t="n">
-        <v>125</v>
+        <v>6</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>121</v>
+        <v>74</v>
       </c>
       <c r="C97" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="C98" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -2191,14 +2158,14 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="C100" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="101">
@@ -2208,23 +2175,36 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="C101" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
+          <t>5225</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>38</v>
+      </c>
+      <c r="C102" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
           <t>2640</t>
         </is>
       </c>
-      <c r="B102" t="n">
-        <v>6</v>
-      </c>
-      <c r="C102" t="n">
-        <v>6</v>
+      <c r="B103" t="n">
+        <v>35</v>
+      </c>
+      <c r="C103" t="n">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/data/台股_警戒掃描.xlsx
+++ b/data/台股_警戒掃描.xlsx
@@ -472,12 +472,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>30d 69080 股, 最新日 20 股</t>
+          <t>30d 60116 股, 最新日 150 股</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -505,12 +505,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>30d 80557 股, 最新日 6 股</t>
+          <t>30d 60679 股, 最新日 48 股</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -538,12 +538,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>30d 201038 股, 最新日 225 股</t>
+          <t>30d 202741 股, 最新日 20 股</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -571,12 +571,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30d 150474 股, 最新日 788 股</t>
+          <t>30d 119392 股, 最新日 735 股</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -604,12 +604,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>30d 73400 股, 最新日 64 股</t>
+          <t>30d 84709 股, 最新日 4 股</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -637,12 +637,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>30d 125391 股, 最新日 388 股</t>
+          <t>30d 125814 股, 最新日 1371 股</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -670,12 +670,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>30d 85674 股, 最新日 76 股</t>
+          <t>30d 62043 股, 最新日 26 股</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -703,12 +703,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>30d 78180 股, 最新日 108 股</t>
+          <t>30d 67039 股, 最新日 727 股</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -736,12 +736,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>30d 145752 股, 最新日 180 股</t>
+          <t>30d 92972 股, 最新日 1165 股</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -769,12 +769,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>30d 72445 股, 最新日 1789 股</t>
+          <t>30d 69544 股, 最新日 2300 股</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -802,12 +802,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>30d 156136 股, 最新日 5 股</t>
+          <t>30d 159505 股, 最新日 7278 股</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -835,12 +835,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>30d 61100 股, 最新日 34 股</t>
+          <t>30d 55690 股, 最新日 39 股</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -861,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C103"/>
+  <dimension ref="A1:C102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,10 +888,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>201038</v>
+        <v>202741</v>
       </c>
       <c r="C2" t="n">
-        <v>225</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -901,75 +901,75 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>156136</v>
+        <v>159505</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>7278</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>150474</v>
+        <v>125814</v>
       </c>
       <c r="C4" t="n">
-        <v>788</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>145752</v>
+        <v>119392</v>
       </c>
       <c r="C5" t="n">
-        <v>180</v>
+        <v>735</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>125391</v>
+        <v>92972</v>
       </c>
       <c r="C6" t="n">
-        <v>388</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>85674</v>
+        <v>84709</v>
       </c>
       <c r="C7" t="n">
-        <v>76</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>80557</v>
+        <v>69544</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="9">
@@ -979,36 +979,36 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>78180</v>
+        <v>67039</v>
       </c>
       <c r="C9" t="n">
-        <v>108</v>
+        <v>727</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>73400</v>
+        <v>62043</v>
       </c>
       <c r="C10" t="n">
-        <v>64</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>72445</v>
+        <v>60679</v>
       </c>
       <c r="C11" t="n">
-        <v>1789</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12">
@@ -1018,10 +1018,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>69080</v>
+        <v>60116</v>
       </c>
       <c r="C12" t="n">
-        <v>20</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13">
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>61100</v>
+        <v>55690</v>
       </c>
       <c r="C13" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>38995</v>
+        <v>28892</v>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24304</v>
+        <v>28605</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16">
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>21487</v>
+        <v>22678</v>
       </c>
       <c r="C16" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -1083,244 +1083,244 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20751</v>
+        <v>18536</v>
       </c>
       <c r="C17" t="n">
-        <v>102</v>
+        <v>190</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16803</v>
+        <v>18261</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16623</v>
+        <v>17945</v>
       </c>
       <c r="C19" t="n">
-        <v>29</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16294</v>
+        <v>17940</v>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15333</v>
+        <v>15464</v>
       </c>
       <c r="C21" t="n">
-        <v>198</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>14074</v>
+        <v>13755</v>
       </c>
       <c r="C22" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13915</v>
+        <v>12050</v>
       </c>
       <c r="C23" t="n">
-        <v>46</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>12674</v>
+        <v>11297</v>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>12624</v>
+        <v>9451</v>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>11916</v>
+        <v>9044</v>
       </c>
       <c r="C26" t="n">
-        <v>232</v>
+        <v>198</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>11192</v>
+        <v>8516</v>
       </c>
       <c r="C27" t="n">
-        <v>23</v>
+        <v>332</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10652</v>
+        <v>8116</v>
       </c>
       <c r="C28" t="n">
-        <v>187</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>9486</v>
+        <v>8060</v>
       </c>
       <c r="C29" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>9379</v>
+        <v>7961</v>
       </c>
       <c r="C30" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>8402</v>
+        <v>7924</v>
       </c>
       <c r="C31" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>8155</v>
+        <v>7890</v>
       </c>
       <c r="C32" t="n">
-        <v>6</v>
+        <v>800</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7576</v>
+        <v>6805</v>
       </c>
       <c r="C33" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>7000</v>
+        <v>6147</v>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>215</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>6806</v>
+        <v>6076</v>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36">
@@ -1330,75 +1330,75 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>6719</v>
+        <v>5214</v>
       </c>
       <c r="C36" t="n">
-        <v>12</v>
+        <v>399</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>6173</v>
+        <v>4994</v>
       </c>
       <c r="C37" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>5766</v>
+        <v>4600</v>
       </c>
       <c r="C38" t="n">
-        <v>156</v>
+        <v>196</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>5462</v>
+        <v>4554</v>
       </c>
       <c r="C39" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>5365</v>
+        <v>4170</v>
       </c>
       <c r="C40" t="n">
-        <v>85</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>5325</v>
+        <v>4000</v>
       </c>
       <c r="C41" t="n">
-        <v>20</v>
+        <v>191</v>
       </c>
     </row>
     <row r="42">
@@ -1408,218 +1408,218 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>5053</v>
+        <v>3848</v>
       </c>
       <c r="C42" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4752</v>
+        <v>3788</v>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>85</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3962</v>
+        <v>3525</v>
       </c>
       <c r="C44" t="n">
-        <v>393</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3840</v>
+        <v>3335</v>
       </c>
       <c r="C45" t="n">
-        <v>40</v>
+        <v>118</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3619</v>
+        <v>3018</v>
       </c>
       <c r="C46" t="n">
-        <v>94</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3526</v>
+        <v>2920</v>
       </c>
       <c r="C47" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3357</v>
+        <v>2903</v>
       </c>
       <c r="C48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3298</v>
+        <v>2886</v>
       </c>
       <c r="C49" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3051</v>
+        <v>2787</v>
       </c>
       <c r="C50" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3006</v>
+        <v>2768</v>
       </c>
       <c r="C51" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3006</v>
+        <v>2701</v>
       </c>
       <c r="C52" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2850</v>
+        <v>2348</v>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2757</v>
+        <v>2283</v>
       </c>
       <c r="C54" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2690</v>
+        <v>2244</v>
       </c>
       <c r="C55" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2612</v>
+        <v>2173</v>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2527</v>
+        <v>2096</v>
       </c>
       <c r="C57" t="n">
-        <v>100</v>
+        <v>35</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2335</v>
+        <v>2089</v>
       </c>
       <c r="C58" t="n">
-        <v>418</v>
+        <v>60</v>
       </c>
     </row>
     <row r="59">
@@ -1629,166 +1629,166 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2106</v>
+        <v>2028</v>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2097</v>
+        <v>2022</v>
       </c>
       <c r="C60" t="n">
-        <v>133</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2060</v>
+        <v>1885</v>
       </c>
       <c r="C61" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2049</v>
+        <v>1836</v>
       </c>
       <c r="C62" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1999</v>
+        <v>1815</v>
       </c>
       <c r="C63" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1925</v>
+        <v>1695</v>
       </c>
       <c r="C64" t="n">
-        <v>6</v>
+        <v>68</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1669</v>
+        <v>1649</v>
       </c>
       <c r="C65" t="n">
-        <v>171</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1600</v>
+        <v>1538</v>
       </c>
       <c r="C66" t="n">
-        <v>6</v>
+        <v>418</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1521</v>
+        <v>1426</v>
       </c>
       <c r="C67" t="n">
-        <v>140</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1512</v>
+        <v>1404</v>
       </c>
       <c r="C68" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1507</v>
+        <v>1325</v>
       </c>
       <c r="C69" t="n">
-        <v>22</v>
+        <v>130</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1372</v>
+        <v>1299</v>
       </c>
       <c r="C70" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1370</v>
+        <v>1203</v>
       </c>
       <c r="C71" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72">
@@ -1798,10 +1798,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1313</v>
+        <v>1202</v>
       </c>
       <c r="C72" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73">
@@ -1811,254 +1811,254 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1091</v>
+        <v>1126</v>
       </c>
       <c r="C73" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>907</v>
+        <v>1088</v>
       </c>
       <c r="C74" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>901</v>
+        <v>930</v>
       </c>
       <c r="C75" t="n">
-        <v>33</v>
+        <v>80</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>805</v>
+        <v>766</v>
       </c>
       <c r="C76" t="n">
-        <v>187</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>769</v>
+        <v>615</v>
       </c>
       <c r="C77" t="n">
-        <v>83</v>
+        <v>8</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>694</v>
+        <v>518</v>
       </c>
       <c r="C78" t="n">
-        <v>502</v>
+        <v>24</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>660</v>
+        <v>502</v>
       </c>
       <c r="C79" t="n">
-        <v>54</v>
+        <v>502</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>648</v>
+        <v>477</v>
       </c>
       <c r="C80" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>472</v>
+        <v>435</v>
       </c>
       <c r="C81" t="n">
-        <v>42</v>
+        <v>152</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="C82" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>336</v>
+        <v>402</v>
       </c>
       <c r="C83" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="C84" t="n">
-        <v>54</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="C85" t="n">
-        <v>16</v>
+        <v>49</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>287</v>
+        <v>185</v>
       </c>
       <c r="C86" t="n">
-        <v>100</v>
+        <v>54</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>262</v>
+        <v>163</v>
       </c>
       <c r="C87" t="n">
-        <v>60</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>258</v>
+        <v>157</v>
       </c>
       <c r="C88" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>181</v>
+        <v>137</v>
       </c>
       <c r="C89" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>163</v>
+        <v>127</v>
       </c>
       <c r="C90" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="C91" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>138</v>
+        <v>94</v>
       </c>
       <c r="C92" t="n">
         <v>5</v>
@@ -2067,92 +2067,92 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>135</v>
+        <v>74</v>
       </c>
       <c r="C93" t="n">
-        <v>37</v>
+        <v>6</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>125</v>
+        <v>66</v>
       </c>
       <c r="C94" t="n">
-        <v>125</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>121</v>
+        <v>62</v>
       </c>
       <c r="C95" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="C96" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="C97" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="C99" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="100">
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="C100" t="n">
         <v>24</v>
@@ -2171,40 +2171,27 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="C101" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="C102" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>2640</t>
-        </is>
-      </c>
-      <c r="B103" t="n">
-        <v>35</v>
-      </c>
-      <c r="C103" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/data/台股_警戒掃描.xlsx
+++ b/data/台股_警戒掃描.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="警戒總覽" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="借券排行" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="減資" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,12 +458,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -472,30 +473,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>30d 60116 股, 最新日 150 股</t>
+          <t>30d 63245 股, 最新日 12 股</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -505,30 +506,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>30d 60679 股, 最新日 48 股</t>
+          <t>30d 200664 股, 最新日 24 股</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -538,30 +539,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>30d 202741 股, 最新日 20 股</t>
+          <t>30d 110479 股, 最新日 524 股</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -571,30 +572,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30d 119392 股, 最新日 735 股</t>
+          <t>30d 78877 股, 最新日 152 股</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -604,12 +605,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>30d 84709 股, 最新日 4 股</t>
+          <t>30d 124726 股, 最新日 114 股</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -622,12 +623,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -637,30 +638,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>30d 125814 股, 最新日 1371 股</t>
+          <t>30d 53866 股, 最新日 25 股</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -670,30 +671,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>30d 62043 股, 最新日 26 股</t>
+          <t>30d 80032 股, 最新日 250 股</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -703,12 +704,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>30d 67039 股, 最新日 727 股</t>
+          <t>30d 145072 股, 最新日 1200 股</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -721,12 +722,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -736,117 +737,51 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>30d 92972 股, 最新日 1165 股</t>
+          <t>30d 56456 股, 最新日 1342 股</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>方土霖</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🪦 借券爆量</t>
+          <t>✂️ 減資</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>30d 69544 股, 最新日 2300 股</t>
+          <t>現金減資</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>3231</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>🪦 借券爆量</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>30d 159505 股, 最新日 7278 股</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>🪦 借券爆量</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>30d 55690 股, 最新日 39 股</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>B</t>
         </is>
       </c>
     </row>
@@ -861,7 +796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C102"/>
+  <dimension ref="A1:C100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,10 +823,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>202741</v>
+        <v>200664</v>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -901,10 +836,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>159505</v>
+        <v>145072</v>
       </c>
       <c r="C3" t="n">
-        <v>7278</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="4">
@@ -914,10 +849,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>125814</v>
+        <v>124726</v>
       </c>
       <c r="C4" t="n">
-        <v>1371</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5">
@@ -927,10 +862,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>119392</v>
+        <v>110479</v>
       </c>
       <c r="C5" t="n">
-        <v>735</v>
+        <v>524</v>
       </c>
     </row>
     <row r="6">
@@ -940,10 +875,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>92972</v>
+        <v>80032</v>
       </c>
       <c r="C6" t="n">
-        <v>1165</v>
+        <v>250</v>
       </c>
     </row>
     <row r="7">
@@ -953,62 +888,62 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>84709</v>
+        <v>78877</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>69544</v>
+        <v>63245</v>
       </c>
       <c r="C8" t="n">
-        <v>2300</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>67039</v>
+        <v>56456</v>
       </c>
       <c r="C9" t="n">
-        <v>727</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>62043</v>
+        <v>53866</v>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>60679</v>
+        <v>48015</v>
       </c>
       <c r="C11" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12">
@@ -1018,88 +953,88 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>60116</v>
+        <v>46275</v>
       </c>
       <c r="C12" t="n">
-        <v>150</v>
+        <v>246</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>55690</v>
+        <v>31724</v>
       </c>
       <c r="C13" t="n">
-        <v>39</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>28892</v>
+        <v>27536</v>
       </c>
       <c r="C14" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28605</v>
+        <v>22027</v>
       </c>
       <c r="C15" t="n">
-        <v>86</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>22678</v>
+        <v>17032</v>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18536</v>
+        <v>16893</v>
       </c>
       <c r="C17" t="n">
-        <v>190</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18261</v>
+        <v>14781</v>
       </c>
       <c r="C18" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
@@ -1109,62 +1044,62 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17945</v>
+        <v>14123</v>
       </c>
       <c r="C19" t="n">
-        <v>119</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17940</v>
+        <v>13703</v>
       </c>
       <c r="C20" t="n">
-        <v>14</v>
+        <v>272</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15464</v>
+        <v>11190</v>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>13755</v>
+        <v>10868</v>
       </c>
       <c r="C22" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>12050</v>
+        <v>9756</v>
       </c>
       <c r="C23" t="n">
-        <v>68</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
@@ -1174,1024 +1109,1062 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>11297</v>
+        <v>9181</v>
       </c>
       <c r="C24" t="n">
-        <v>34</v>
+        <v>173</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>9451</v>
+        <v>8192</v>
       </c>
       <c r="C25" t="n">
-        <v>10</v>
+        <v>303</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>9044</v>
+        <v>8166</v>
       </c>
       <c r="C26" t="n">
-        <v>198</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8516</v>
+        <v>7226</v>
       </c>
       <c r="C27" t="n">
-        <v>332</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>8116</v>
+        <v>6561</v>
       </c>
       <c r="C28" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>8060</v>
+        <v>6185</v>
       </c>
       <c r="C29" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7961</v>
+        <v>6068</v>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>180</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7924</v>
+        <v>5952</v>
       </c>
       <c r="C31" t="n">
-        <v>10</v>
+        <v>188</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>7890</v>
+        <v>5802</v>
       </c>
       <c r="C32" t="n">
-        <v>800</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>6805</v>
+        <v>5438</v>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>6147</v>
+        <v>5240</v>
       </c>
       <c r="C34" t="n">
-        <v>215</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>6076</v>
+        <v>4923</v>
       </c>
       <c r="C35" t="n">
-        <v>45</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>5214</v>
+        <v>4749</v>
       </c>
       <c r="C36" t="n">
-        <v>399</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4994</v>
+        <v>4667</v>
       </c>
       <c r="C37" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4600</v>
+        <v>4026</v>
       </c>
       <c r="C38" t="n">
-        <v>196</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4554</v>
+        <v>3723</v>
       </c>
       <c r="C39" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4170</v>
+        <v>3720</v>
       </c>
       <c r="C40" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4000</v>
+        <v>3465</v>
       </c>
       <c r="C41" t="n">
-        <v>191</v>
+        <v>26</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3848</v>
+        <v>3308</v>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3788</v>
+        <v>3267</v>
       </c>
       <c r="C43" t="n">
-        <v>85</v>
+        <v>34</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3525</v>
+        <v>2990</v>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3335</v>
+        <v>2920</v>
       </c>
       <c r="C45" t="n">
-        <v>118</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3018</v>
+        <v>2811</v>
       </c>
       <c r="C46" t="n">
-        <v>2117</v>
+        <v>200</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2920</v>
+        <v>2723</v>
       </c>
       <c r="C47" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2903</v>
+        <v>2700</v>
       </c>
       <c r="C48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2886</v>
+        <v>2587</v>
       </c>
       <c r="C49" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2787</v>
+        <v>2508</v>
       </c>
       <c r="C50" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2768</v>
+        <v>2454</v>
       </c>
       <c r="C51" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2701</v>
+        <v>2444</v>
       </c>
       <c r="C52" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2348</v>
+        <v>2346</v>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>215</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2283</v>
+        <v>2119</v>
       </c>
       <c r="C54" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2244</v>
+        <v>1895</v>
       </c>
       <c r="C55" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2173</v>
+        <v>1830</v>
       </c>
       <c r="C56" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2096</v>
+        <v>1695</v>
       </c>
       <c r="C57" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2089</v>
+        <v>1632</v>
       </c>
       <c r="C58" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2028</v>
+        <v>1604</v>
       </c>
       <c r="C59" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2022</v>
+        <v>1594</v>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1885</v>
+        <v>1566</v>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1836</v>
+        <v>1533</v>
       </c>
       <c r="C62" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1815</v>
+        <v>1305</v>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>173</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1695</v>
+        <v>1264</v>
       </c>
       <c r="C64" t="n">
-        <v>68</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1649</v>
+        <v>1247</v>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1538</v>
+        <v>1089</v>
       </c>
       <c r="C66" t="n">
-        <v>418</v>
+        <v>164</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1426</v>
+        <v>1057</v>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>80</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1404</v>
+        <v>1012</v>
       </c>
       <c r="C68" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1325</v>
+        <v>990</v>
       </c>
       <c r="C69" t="n">
-        <v>130</v>
+        <v>26</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1299</v>
+        <v>971</v>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1203</v>
+        <v>930</v>
       </c>
       <c r="C71" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1202</v>
+        <v>919</v>
       </c>
       <c r="C72" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1126</v>
+        <v>740</v>
       </c>
       <c r="C73" t="n">
-        <v>50</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1088</v>
+        <v>580</v>
       </c>
       <c r="C74" t="n">
-        <v>60</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>930</v>
+        <v>550</v>
       </c>
       <c r="C75" t="n">
-        <v>80</v>
+        <v>8</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>766</v>
+        <v>500</v>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>615</v>
+        <v>479</v>
       </c>
       <c r="C77" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>518</v>
+        <v>428</v>
       </c>
       <c r="C78" t="n">
-        <v>24</v>
+        <v>150</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>502</v>
+        <v>373</v>
       </c>
       <c r="C79" t="n">
-        <v>502</v>
+        <v>8</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>477</v>
+        <v>344</v>
       </c>
       <c r="C80" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>435</v>
+        <v>341</v>
       </c>
       <c r="C81" t="n">
-        <v>152</v>
+        <v>88</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>425</v>
+        <v>331</v>
       </c>
       <c r="C82" t="n">
-        <v>88</v>
+        <v>58</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>402</v>
+        <v>329</v>
       </c>
       <c r="C83" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>295</v>
+        <v>282</v>
       </c>
       <c r="C84" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="C85" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>185</v>
+        <v>242</v>
       </c>
       <c r="C86" t="n">
-        <v>54</v>
+        <v>226</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>163</v>
+        <v>198</v>
       </c>
       <c r="C87" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>157</v>
+        <v>183</v>
       </c>
       <c r="C88" t="n">
-        <v>42</v>
+        <v>62</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="C89" t="n">
-        <v>6</v>
+        <v>54</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="C90" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="C91" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="C92" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="C93" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="C95" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="C96" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="C97" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C98" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="C99" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C100" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>5519</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>16</v>
-      </c>
-      <c r="C101" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>6263</t>
-        </is>
-      </c>
-      <c r="B102" t="n">
-        <v>5</v>
-      </c>
-      <c r="C102" t="n">
-        <v>5</v>
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>代號</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>原因</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>減資前</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>減資後參考價</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>4527</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>現金減資</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="E2" t="n">
+        <v>44.33</v>
       </c>
     </row>
   </sheetData>

--- a/data/台股_警戒掃描.xlsx
+++ b/data/台股_警戒掃描.xlsx
@@ -458,12 +458,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -473,30 +473,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>30d 63245 股, 最新日 12 股</t>
+          <t>30d 101351 股, 最新日 1004 股</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -506,30 +506,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>30d 200664 股, 最新日 24 股</t>
+          <t>30d 61220 股, 最新日 25 股</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -539,30 +539,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>30d 110479 股, 最新日 524 股</t>
+          <t>30d 207042 股, 最新日 4 股</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -572,30 +572,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30d 78877 股, 最新日 152 股</t>
+          <t>30d 107355 股, 最新日 71 股</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -605,12 +605,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>30d 124726 股, 最新日 114 股</t>
+          <t>30d 134525 股, 最新日 27 股</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -623,12 +623,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -638,30 +638,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>30d 53866 股, 最新日 25 股</t>
+          <t>30d 131373 股, 最新日 541 股</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -671,30 +671,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>30d 80032 股, 最新日 250 股</t>
+          <t>30d 93192 股, 最新日 311 股</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -704,30 +704,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>30d 145072 股, 最新日 1200 股</t>
+          <t>30d 74323 股, 最新日 2355 股</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -737,18 +737,18 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>30d 56456 股, 最新日 1342 股</t>
+          <t>30d 133558 股, 最新日 1584 股</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C100"/>
+  <dimension ref="A1:C98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -823,111 +823,111 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>200664</v>
+        <v>207042</v>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>145072</v>
+        <v>134525</v>
       </c>
       <c r="C3" t="n">
-        <v>1200</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>124726</v>
+        <v>133558</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>110479</v>
+        <v>131373</v>
       </c>
       <c r="C5" t="n">
-        <v>524</v>
+        <v>541</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>80032</v>
+        <v>107355</v>
       </c>
       <c r="C6" t="n">
-        <v>250</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>78877</v>
+        <v>101351</v>
       </c>
       <c r="C7" t="n">
-        <v>152</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>63245</v>
+        <v>93192</v>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>311</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>56456</v>
+        <v>74323</v>
       </c>
       <c r="C9" t="n">
-        <v>1342</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>53866</v>
+        <v>61220</v>
       </c>
       <c r="C10" t="n">
         <v>25</v>
@@ -936,27 +936,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>48015</v>
+        <v>41410</v>
       </c>
       <c r="C11" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>46275</v>
+        <v>40754</v>
       </c>
       <c r="C12" t="n">
-        <v>246</v>
+        <v>954</v>
       </c>
     </row>
     <row r="13">
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31724</v>
+        <v>33708</v>
       </c>
       <c r="C13" t="n">
-        <v>1058</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="14">
@@ -979,23 +979,23 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>27536</v>
+        <v>27850</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>913</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22027</v>
+        <v>25746</v>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
@@ -1005,569 +1005,569 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17032</v>
+        <v>21847</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16893</v>
+        <v>18001</v>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14781</v>
+        <v>17543</v>
       </c>
       <c r="C18" t="n">
-        <v>20</v>
+        <v>5819</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14123</v>
+        <v>14853</v>
       </c>
       <c r="C19" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13703</v>
+        <v>13982</v>
       </c>
       <c r="C20" t="n">
-        <v>272</v>
+        <v>339</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11190</v>
+        <v>13275</v>
       </c>
       <c r="C21" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10868</v>
+        <v>13027</v>
       </c>
       <c r="C22" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9756</v>
+        <v>10953</v>
       </c>
       <c r="C23" t="n">
-        <v>15</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9181</v>
+        <v>9257</v>
       </c>
       <c r="C24" t="n">
-        <v>173</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>8192</v>
+        <v>8816</v>
       </c>
       <c r="C25" t="n">
-        <v>303</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>8166</v>
+        <v>8649</v>
       </c>
       <c r="C26" t="n">
-        <v>15</v>
+        <v>178</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7226</v>
+        <v>8401</v>
       </c>
       <c r="C27" t="n">
-        <v>79</v>
+        <v>188</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6561</v>
+        <v>8149</v>
       </c>
       <c r="C28" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>6185</v>
+        <v>8056</v>
       </c>
       <c r="C29" t="n">
-        <v>21</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>6068</v>
+        <v>7452</v>
       </c>
       <c r="C30" t="n">
-        <v>180</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5952</v>
+        <v>6736</v>
       </c>
       <c r="C31" t="n">
-        <v>188</v>
+        <v>2583</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5802</v>
+        <v>6131</v>
       </c>
       <c r="C32" t="n">
-        <v>7</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5438</v>
+        <v>5921</v>
       </c>
       <c r="C33" t="n">
-        <v>28</v>
+        <v>188</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>5240</v>
+        <v>5807</v>
       </c>
       <c r="C34" t="n">
-        <v>11</v>
+        <v>304</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4923</v>
+        <v>5179</v>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4749</v>
+        <v>5094</v>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4667</v>
+        <v>5070</v>
       </c>
       <c r="C37" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4026</v>
+        <v>4590</v>
       </c>
       <c r="C38" t="n">
-        <v>13</v>
+        <v>105</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3723</v>
+        <v>4173</v>
       </c>
       <c r="C39" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3720</v>
+        <v>3885</v>
       </c>
       <c r="C40" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3465</v>
+        <v>3439</v>
       </c>
       <c r="C41" t="n">
-        <v>26</v>
+        <v>58</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3308</v>
+        <v>3271</v>
       </c>
       <c r="C42" t="n">
-        <v>1469</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3267</v>
+        <v>2995</v>
       </c>
       <c r="C43" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2990</v>
+        <v>2916</v>
       </c>
       <c r="C44" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2920</v>
+        <v>2812</v>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2811</v>
+        <v>2686</v>
       </c>
       <c r="C46" t="n">
-        <v>200</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2723</v>
+        <v>2544</v>
       </c>
       <c r="C47" t="n">
-        <v>5</v>
+        <v>523</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2700</v>
+        <v>2473</v>
       </c>
       <c r="C48" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2587</v>
+        <v>2438</v>
       </c>
       <c r="C49" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2508</v>
+        <v>2380</v>
       </c>
       <c r="C50" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2454</v>
+        <v>2341</v>
       </c>
       <c r="C51" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2444</v>
+        <v>2234</v>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2346</v>
+        <v>2221</v>
       </c>
       <c r="C53" t="n">
-        <v>215</v>
+        <v>66</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2119</v>
+        <v>2174</v>
       </c>
       <c r="C54" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1895</v>
+        <v>2133</v>
       </c>
       <c r="C55" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1830</v>
+        <v>1933</v>
       </c>
       <c r="C56" t="n">
-        <v>35</v>
+        <v>104</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1695</v>
+        <v>1926</v>
       </c>
       <c r="C57" t="n">
-        <v>31</v>
+        <v>78</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1632</v>
+        <v>1805</v>
       </c>
       <c r="C58" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1604</v>
+        <v>1661</v>
       </c>
       <c r="C59" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="60">
@@ -1577,244 +1577,244 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1594</v>
+        <v>1661</v>
       </c>
       <c r="C60" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1566</v>
+        <v>1620</v>
       </c>
       <c r="C61" t="n">
-        <v>30</v>
+        <v>235</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1533</v>
+        <v>1609</v>
       </c>
       <c r="C62" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1305</v>
+        <v>1562</v>
       </c>
       <c r="C63" t="n">
-        <v>173</v>
+        <v>46</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1264</v>
+        <v>1557</v>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>119</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1247</v>
+        <v>1481</v>
       </c>
       <c r="C65" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1089</v>
+        <v>1381</v>
       </c>
       <c r="C66" t="n">
-        <v>164</v>
+        <v>57</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1057</v>
+        <v>1275</v>
       </c>
       <c r="C67" t="n">
-        <v>80</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1012</v>
+        <v>1081</v>
       </c>
       <c r="C68" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>990</v>
+        <v>1046</v>
       </c>
       <c r="C69" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>971</v>
+        <v>1045</v>
       </c>
       <c r="C70" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>930</v>
+        <v>866</v>
       </c>
       <c r="C71" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>919</v>
+        <v>859</v>
       </c>
       <c r="C72" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>740</v>
+        <v>661</v>
       </c>
       <c r="C73" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>580</v>
+        <v>545</v>
       </c>
       <c r="C74" t="n">
-        <v>3</v>
+        <v>84</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>550</v>
+        <v>508</v>
       </c>
       <c r="C75" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>500</v>
+        <v>487</v>
       </c>
       <c r="C76" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>479</v>
+        <v>428</v>
       </c>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>150</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>428</v>
+        <v>402</v>
       </c>
       <c r="C78" t="n">
-        <v>150</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -1824,114 +1824,114 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C79" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>344</v>
+        <v>367</v>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>341</v>
+        <v>298</v>
       </c>
       <c r="C81" t="n">
-        <v>88</v>
+        <v>10</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>331</v>
+        <v>296</v>
       </c>
       <c r="C82" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>329</v>
+        <v>273</v>
       </c>
       <c r="C83" t="n">
-        <v>80</v>
+        <v>58</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>282</v>
+        <v>253</v>
       </c>
       <c r="C84" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="C85" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C86" t="n">
-        <v>226</v>
+        <v>44</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="C87" t="n">
-        <v>41</v>
+        <v>226</v>
       </c>
     </row>
     <row r="88">
@@ -1941,10 +1941,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>183</v>
+        <v>125</v>
       </c>
       <c r="C88" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="89">
@@ -1954,72 +1954,72 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>54</v>
+        <v>20</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>141</v>
+        <v>101</v>
       </c>
       <c r="C90" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="C91" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>61</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C93" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C94" t="n">
         <v>29</v>
@@ -2028,79 +2028,53 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="C95" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="C96" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C97" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C98" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>1618</t>
-        </is>
-      </c>
-      <c r="B99" t="n">
-        <v>5</v>
-      </c>
-      <c r="C99" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>5225</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>3</v>
-      </c>
-      <c r="C100" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/台股_警戒掃描.xlsx
+++ b/data/台股_警戒掃描.xlsx
@@ -473,12 +473,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>30d 101351 股, 最新日 1004 股</t>
+          <t>30d 129168 股, 最新日 224 股</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -506,12 +506,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>30d 61220 股, 最新日 25 股</t>
+          <t>30d 51087 股, 最新日 600 股</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -539,12 +539,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>30d 207042 股, 最新日 4 股</t>
+          <t>30d 73643 股, 最新日 41 股</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -572,12 +572,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30d 107355 股, 最新日 71 股</t>
+          <t>30d 113142 股, 最新日 25 股</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -605,12 +605,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>30d 134525 股, 最新日 27 股</t>
+          <t>30d 126611 股, 最新日 989 股</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -638,12 +638,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>30d 131373 股, 最新日 541 股</t>
+          <t>30d 86583 股, 最新日 90 股</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -671,12 +671,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>30d 93192 股, 最新日 311 股</t>
+          <t>30d 99135 股, 最新日 228 股</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>30d 74323 股, 最新日 2355 股</t>
+          <t>30d 90491 股, 最新日 798 股</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -737,12 +737,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>30d 133558 股, 最新日 1584 股</t>
+          <t>30d 117377 股, 最新日 114 股</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -796,7 +796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C98"/>
+  <dimension ref="A1:C96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -819,14 +819,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>207042</v>
+        <v>129168</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3">
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>134525</v>
+        <v>126611</v>
       </c>
       <c r="C3" t="n">
-        <v>27</v>
+        <v>989</v>
       </c>
     </row>
     <row r="4">
@@ -849,75 +849,75 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>133558</v>
+        <v>117377</v>
       </c>
       <c r="C4" t="n">
-        <v>1584</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>131373</v>
+        <v>113142</v>
       </c>
       <c r="C5" t="n">
-        <v>541</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>107355</v>
+        <v>99135</v>
       </c>
       <c r="C6" t="n">
-        <v>71</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>101351</v>
+        <v>90491</v>
       </c>
       <c r="C7" t="n">
-        <v>1004</v>
+        <v>798</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>93192</v>
+        <v>86583</v>
       </c>
       <c r="C8" t="n">
-        <v>311</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>74323</v>
+        <v>73643</v>
       </c>
       <c r="C9" t="n">
-        <v>2355</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
@@ -927,257 +927,257 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>61220</v>
+        <v>51087</v>
       </c>
       <c r="C10" t="n">
-        <v>25</v>
+        <v>600</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>41410</v>
+        <v>38728</v>
       </c>
       <c r="C11" t="n">
-        <v>68</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>40754</v>
+        <v>36192</v>
       </c>
       <c r="C12" t="n">
-        <v>954</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>33708</v>
+        <v>33371</v>
       </c>
       <c r="C13" t="n">
-        <v>1445</v>
+        <v>556</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>27850</v>
+        <v>33280</v>
       </c>
       <c r="C14" t="n">
-        <v>913</v>
+        <v>378</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25746</v>
+        <v>32212</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>378</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>21847</v>
+        <v>28909</v>
       </c>
       <c r="C16" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18001</v>
+        <v>23604</v>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>185</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17543</v>
+        <v>21431</v>
       </c>
       <c r="C18" t="n">
-        <v>5819</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14853</v>
+        <v>17635</v>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>159</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13982</v>
+        <v>13874</v>
       </c>
       <c r="C20" t="n">
-        <v>339</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13275</v>
+        <v>13543</v>
       </c>
       <c r="C21" t="n">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>13027</v>
+        <v>12901</v>
       </c>
       <c r="C22" t="n">
-        <v>101</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10953</v>
+        <v>9687</v>
       </c>
       <c r="C23" t="n">
-        <v>287</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9257</v>
+        <v>9335</v>
       </c>
       <c r="C24" t="n">
-        <v>12</v>
+        <v>160</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>8816</v>
+        <v>8192</v>
       </c>
       <c r="C25" t="n">
-        <v>20</v>
+        <v>151</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>8649</v>
+        <v>8130</v>
       </c>
       <c r="C26" t="n">
-        <v>178</v>
+        <v>455</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8401</v>
+        <v>8021</v>
       </c>
       <c r="C27" t="n">
-        <v>188</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>8149</v>
+        <v>7825</v>
       </c>
       <c r="C28" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>8056</v>
+        <v>7798</v>
       </c>
       <c r="C29" t="n">
-        <v>109</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30">
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7452</v>
+        <v>7781</v>
       </c>
       <c r="C30" t="n">
         <v>100</v>
@@ -1196,14 +1196,14 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>6736</v>
+        <v>7393</v>
       </c>
       <c r="C31" t="n">
-        <v>2583</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -1213,140 +1213,140 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>6131</v>
+        <v>7149</v>
       </c>
       <c r="C32" t="n">
-        <v>2053</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5921</v>
+        <v>6447</v>
       </c>
       <c r="C33" t="n">
-        <v>188</v>
+        <v>26</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>5807</v>
+        <v>6413</v>
       </c>
       <c r="C34" t="n">
-        <v>304</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>5179</v>
+        <v>6341</v>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>99</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>5094</v>
+        <v>5631</v>
       </c>
       <c r="C36" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>5070</v>
+        <v>4603</v>
       </c>
       <c r="C37" t="n">
-        <v>42</v>
+        <v>187</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4590</v>
+        <v>4463</v>
       </c>
       <c r="C38" t="n">
-        <v>105</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4173</v>
+        <v>4273</v>
       </c>
       <c r="C39" t="n">
-        <v>100</v>
+        <v>423</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3885</v>
+        <v>4203</v>
       </c>
       <c r="C40" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3439</v>
+        <v>4192</v>
       </c>
       <c r="C41" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3271</v>
+        <v>4164</v>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43">
@@ -1356,257 +1356,257 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2995</v>
+        <v>3938</v>
       </c>
       <c r="C43" t="n">
-        <v>8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2916</v>
+        <v>3617</v>
       </c>
       <c r="C44" t="n">
-        <v>34</v>
+        <v>705</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2812</v>
+        <v>3448</v>
       </c>
       <c r="C45" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2686</v>
+        <v>3084</v>
       </c>
       <c r="C46" t="n">
-        <v>8</v>
+        <v>54</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2544</v>
+        <v>3054</v>
       </c>
       <c r="C47" t="n">
-        <v>523</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2473</v>
+        <v>3000</v>
       </c>
       <c r="C48" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2438</v>
+        <v>2825</v>
       </c>
       <c r="C49" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2380</v>
+        <v>2727</v>
       </c>
       <c r="C50" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2341</v>
+        <v>2576</v>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2234</v>
+        <v>2439</v>
       </c>
       <c r="C52" t="n">
-        <v>4</v>
+        <v>200</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2221</v>
+        <v>2214</v>
       </c>
       <c r="C53" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2174</v>
+        <v>2199</v>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2133</v>
+        <v>2174</v>
       </c>
       <c r="C55" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1933</v>
+        <v>2117</v>
       </c>
       <c r="C56" t="n">
-        <v>104</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1926</v>
+        <v>2065</v>
       </c>
       <c r="C57" t="n">
-        <v>78</v>
+        <v>118</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1805</v>
+        <v>1936</v>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1661</v>
+        <v>1895</v>
       </c>
       <c r="C59" t="n">
-        <v>13</v>
+        <v>170</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1661</v>
+        <v>1816</v>
       </c>
       <c r="C60" t="n">
-        <v>4</v>
+        <v>439</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1620</v>
+        <v>1770</v>
       </c>
       <c r="C61" t="n">
-        <v>235</v>
+        <v>24</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1609</v>
+        <v>1750</v>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -1616,228 +1616,228 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1562</v>
+        <v>1731</v>
       </c>
       <c r="C63" t="n">
-        <v>46</v>
+        <v>349</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1557</v>
+        <v>1687</v>
       </c>
       <c r="C64" t="n">
-        <v>119</v>
+        <v>332</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1481</v>
+        <v>1595</v>
       </c>
       <c r="C65" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1381</v>
+        <v>1510</v>
       </c>
       <c r="C66" t="n">
-        <v>57</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1275</v>
+        <v>1468</v>
       </c>
       <c r="C67" t="n">
-        <v>9</v>
+        <v>120</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1081</v>
+        <v>1357</v>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1046</v>
+        <v>1252</v>
       </c>
       <c r="C69" t="n">
-        <v>5</v>
+        <v>71</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1045</v>
+        <v>1234</v>
       </c>
       <c r="C70" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>866</v>
+        <v>1222</v>
       </c>
       <c r="C71" t="n">
-        <v>8</v>
+        <v>120</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>859</v>
+        <v>786</v>
       </c>
       <c r="C72" t="n">
-        <v>6</v>
+        <v>56</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>661</v>
+        <v>607</v>
       </c>
       <c r="C73" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>545</v>
+        <v>568</v>
       </c>
       <c r="C74" t="n">
-        <v>84</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>508</v>
+        <v>538</v>
       </c>
       <c r="C75" t="n">
-        <v>3</v>
+        <v>75</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>487</v>
+        <v>527</v>
       </c>
       <c r="C76" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>428</v>
+        <v>470</v>
       </c>
       <c r="C77" t="n">
-        <v>150</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>402</v>
+        <v>381</v>
       </c>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>370</v>
+        <v>344</v>
       </c>
       <c r="C79" t="n">
-        <v>20</v>
+        <v>86</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>367</v>
+        <v>314</v>
       </c>
       <c r="C80" t="n">
         <v>1</v>
@@ -1846,53 +1846,53 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C81" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>296</v>
+        <v>233</v>
       </c>
       <c r="C82" t="n">
-        <v>37</v>
+        <v>60</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>273</v>
+        <v>228</v>
       </c>
       <c r="C83" t="n">
-        <v>58</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>253</v>
+        <v>216</v>
       </c>
       <c r="C84" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="85">
@@ -1902,36 +1902,36 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>252</v>
+        <v>197</v>
       </c>
       <c r="C85" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>245</v>
+        <v>187</v>
       </c>
       <c r="C86" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>242</v>
+        <v>165</v>
       </c>
       <c r="C87" t="n">
-        <v>226</v>
+        <v>55</v>
       </c>
     </row>
     <row r="88">
@@ -1950,40 +1950,40 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="C89" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="C90" t="n">
-        <v>39</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C91" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -2002,79 +2002,53 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="C93" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="C94" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C96" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>6739</t>
-        </is>
-      </c>
-      <c r="B97" t="n">
-        <v>4</v>
-      </c>
-      <c r="C97" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>4129</t>
-        </is>
-      </c>
-      <c r="B98" t="n">
-        <v>1</v>
-      </c>
-      <c r="C98" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
